--- a/results/tables/benchmark_smoke/benchmark_summary.xlsx
+++ b/results/tables/benchmark_smoke/benchmark_summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="benchmark_summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="benchmark_summary" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -615,16 +615,16 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>501429.0625</v>
+        <v>550888.5657085751</v>
       </c>
       <c r="I2" t="n">
-        <v>0.258107600006042</v>
+        <v>0.3470234500127845</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>501429.0625</v>
+        <v>550888.5657085751</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
@@ -636,7 +636,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.04169455135535822</v>
+        <v>0.05102673452020245</v>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
@@ -679,16 +679,16 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>501429.0625</v>
+        <v>550888.565708575</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04998000000341563</v>
+        <v>0.05321424995781854</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>501429.0625</v>
+        <v>550888.565708575</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
@@ -698,13 +698,13 @@
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>62197.11247316872</v>
+        <v>62197.11247316866</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01388955707500959</v>
+        <v>0.01465033319894115</v>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
@@ -747,32 +747,32 @@
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>501429.0625</v>
+        <v>550888.5657086438</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01504730000306154</v>
+        <v>0.01714255003025755</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2.126783346519369e-16</v>
       </c>
       <c r="K4" t="n">
-        <v>501429.0625</v>
+        <v>550888.5657086439</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>55.5</v>
+        <v>57</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
         <v>62197.11247316872</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.401207635147903e-17</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.003779910011157565</v>
+        <v>0.005846005376074193</v>
       </c>
       <c r="R4" t="n">
         <v>2</v>
@@ -793,16 +793,16 @@
         <v>276147.33046875</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>98919.00641728763</v>
       </c>
       <c r="Y4" t="n">
-        <v>821928.125</v>
+        <v>920847.1314172876</v>
       </c>
       <c r="Z4" t="n">
         <v>180930</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.91038304567337e-11</v>
       </c>
       <c r="AB4" t="n">
         <v>1</v>
